--- a/Excel_projects/2025.xlsx
+++ b/Excel_projects/2025.xlsx
@@ -8,21 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thano\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768F808B-CF2E-4439-920F-5B2EDD2E3AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A353F76A-689C-45DA-AF49-6E043B759863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="1" r:id="rId1"/>
     <sheet name="Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="Pivot_Category" sheetId="3" r:id="rId3"/>
+    <sheet name="pivot_user" sheetId="4" r:id="rId4"/>
+    <sheet name="dashboard" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Analysis!$A$2:$P$368</definedName>
+    <definedName name="_xlcn.WorksheetConnection_2025.xlsxTransactions_tbl1" hidden="1">Transactions_tbl[]</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="43" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
+      <x15:dataModel>
+        <x15:modelTables>
+          <x15:modelTable id="Transactions_tbl" name="Transactions_tbl" connection="WorksheetConnection_2025.xlsx!Transactions_tbl"/>
+        </x15:modelTables>
+      </x15:dataModel>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,8 +54,31 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{DC4A789E-8DFD-437A-B066-DAA2EE7D64EF}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
+    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+    <extLst>
+      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
+        <x15:connection id="" model="1"/>
+      </ext>
+    </extLst>
+  </connection>
+  <connection id="2" xr16:uid="{F1095852-D539-4779-87B0-93D75D6EB732}" name="WorksheetConnection_2025.xlsx!Transactions_tbl" type="102" refreshedVersion="8" minRefreshableVersion="5">
+    <extLst>
+      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
+        <x15:connection id="Transactions_tbl" autoDelete="1">
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_2025.xlsxTransactions_tbl1"/>
+        </x15:connection>
+      </ext>
+    </extLst>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -92,17 +130,44 @@
   <si>
     <t>Average Transactions</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>Count of Amount</t>
+  </si>
+  <si>
+    <t>Who are the most active users?</t>
+  </si>
+  <si>
+    <t>Which category generates the most revenue?</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>Transaction Perfomance Overview</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;XDR&quot;_-;\-* #,##0.00\ &quot;XDR&quot;_-;_-* &quot;-&quot;??\ &quot;XDR&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="&quot; &quot;* #,##0.00&quot; &quot;[$€-408]&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;[$€-408]&quot; &quot;;&quot; &quot;* &quot;-&quot;#&quot; &quot;[$€-408]&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot; &quot;* #,##0.00&quot; &quot;[$€]&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;[$€]&quot; &quot;;&quot; &quot;* &quot;-&quot;#&quot; &quot;[$€]&quot; &quot;;&quot; &quot;@&quot; &quot;" x16r2:formatCode16="&quot; &quot;* #,##0.00&quot; &quot;[$€-en-150]&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;[$€-en-150]&quot; &quot;;&quot; &quot;* &quot;-&quot;#&quot; &quot;[$€-en-150]&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot; &quot;* #,##0.00&quot; &quot;[$€-408]&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;[$€-408]&quot; &quot;;&quot; &quot;* &quot;-&quot;#&quot; &quot;[$€-408]&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot; &quot;* #,##0.00&quot; &quot;[$€]&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;[$€]&quot; &quot;;&quot; &quot;* &quot;-&quot;#&quot; &quot;[$€]&quot; &quot;;&quot; &quot;@&quot; &quot;" x16r2:formatCode16="&quot; &quot;* #,##0.00&quot; &quot;[$€-en-150]&quot; &quot;;&quot;-&quot;* #,##0.00&quot; &quot;[$€-en-150]&quot; &quot;;&quot; &quot;* &quot;-&quot;#&quot; &quot;[$€-en-150]&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
+    <numFmt numFmtId="166" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-408]"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ [$€-408]_-;\-* #,##0.00\ [$€-408]_-;_-* &quot;-&quot;??\ [$€-408]_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +193,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -178,7 +251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -292,57 +365,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -351,12 +451,318 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="22">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-* #,##0.00\ [$€-408]_-;\-* #,##0.00\ [$€-408]_-;_-* &quot;-&quot;??\ [$€-408]_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-408]"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -390,18 +796,1529 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[2025.xlsx]Pivot_Category!PivotTable1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue by Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Category!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Category!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Crypto</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DeFi</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NFT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Category!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00\ [$€-408]</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-077A-4C37-ACDA-76FD662E5091}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1795191072"/>
+        <c:axId val="1795191552"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1795191072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1795191552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1795191552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00\ [$€-408]" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1795191072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B131AB07-C7DC-4C2F-8B4F-87DD927CCB6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="thanos gourgouvelas" refreshedDate="46027.575505208333" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{17E716A6-6A1A-437F-8B41-DE0897A0504A}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Transactions_tbl"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2024-01-05T00:00:00"/>
+    </cacheField>
+    <cacheField name="User_ID" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30" maxValue="500"/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Crypto"/>
+        <s v="NFT"/>
+        <s v="DeFi"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="High_Value" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Category_Flag" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="thanos gourgouvelas" refreshedDate="46027.590097685184" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{A9B56FA2-9908-4040-826C-867435928940}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Transactions_tbl].[User_ID].[User_ID]" caption="User_ID" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems count="3">
+        <s v="U001"/>
+        <s v="U002"/>
+        <s v="U003"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Amount]" caption="Sum of Amount" numFmtId="0" hierarchy="8" level="32767"/>
+    <cacheField name="[Measures].[Count of Amount]" caption="Count of Amount" numFmtId="0" hierarchy="9" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="10">
+    <cacheHierarchy uniqueName="[Transactions_tbl].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Transactions_tbl].[Date].[All]" allUniqueName="[Transactions_tbl].[Date].[All]" dimensionUniqueName="[Transactions_tbl]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions_tbl].[User_ID]" caption="User_ID" attribute="1" defaultMemberUniqueName="[Transactions_tbl].[User_ID].[All]" allUniqueName="[Transactions_tbl].[User_ID].[All]" dimensionUniqueName="[Transactions_tbl]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions_tbl].[Amount]" caption="Amount" attribute="1" defaultMemberUniqueName="[Transactions_tbl].[Amount].[All]" allUniqueName="[Transactions_tbl].[Amount].[All]" dimensionUniqueName="[Transactions_tbl]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions_tbl].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Transactions_tbl].[Category].[All]" allUniqueName="[Transactions_tbl].[Category].[All]" dimensionUniqueName="[Transactions_tbl]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions_tbl].[High_Value]" caption="High_Value" attribute="1" defaultMemberUniqueName="[Transactions_tbl].[High_Value].[All]" allUniqueName="[Transactions_tbl].[High_Value].[All]" dimensionUniqueName="[Transactions_tbl]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions_tbl].[Category_Flag]" caption="Category_Flag" attribute="1" defaultMemberUniqueName="[Transactions_tbl].[Category_Flag].[All]" allUniqueName="[Transactions_tbl].[Category_Flag].[All]" dimensionUniqueName="[Transactions_tbl]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions_tbl]" caption="__XL_Count Transactions_tbl" measure="1" displayFolder="" measureGroup="Transactions_tbl" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Amount]" caption="Sum of Amount" measure="1" displayFolder="" measureGroup="Transactions_tbl" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Amount]" caption="Count of Amount" measure="1" displayFolder="" measureGroup="Transactions_tbl" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions_tbl" uniqueName="[Transactions_tbl]" caption="Transactions_tbl"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Transactions_tbl" caption="Transactions_tbl"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+  <r>
+    <d v="2024-01-01T00:00:00"/>
+    <s v="U001"/>
+    <n v="120"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <d v="2024-01-02T00:00:00"/>
+    <s v="U002"/>
+    <n v="50"/>
+    <x v="1"/>
+    <s v="No"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <d v="2024-01-02T00:00:00"/>
+    <s v="U001"/>
+    <n v="200"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <d v="2024-01-03T00:00:00"/>
+    <s v="U003"/>
+    <n v="75"/>
+    <x v="2"/>
+    <s v="No"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <d v="2024-01-03T00:00:00"/>
+    <s v="U002"/>
+    <n v="30"/>
+    <x v="1"/>
+    <s v="No"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <d v="2024-01-04T00:00:00"/>
+    <s v="U001"/>
+    <n v="500"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ECDBFDB5-031D-4EE6-A528-4E0C63D17EF5}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="2" baseField="0" baseItem="0" numFmtId="168"/>
+  </dataFields>
+  <formats count="7">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{06C362F7-92E4-4438-BB20-8E3667ABD9A1}" name="PivotTable2" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:C6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Amount" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Count of Amount" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotHierarchies count="10">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Amount"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_2025.xlsx!Transactions_tbl">
+        <x15:activeTabTopLevelEntity name="[Transactions_tbl]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E70C6BD0-8AFF-43B7-8C0E-B4752FBD644A}" name="Transactions_tbl" displayName="Transactions_tbl" ref="A1:F7" totalsRowShown="0">
   <autoFilter ref="A1:F7" xr:uid="{E70C6BD0-8AFF-43B7-8C0E-B4752FBD644A}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{43B3B1A1-A8DB-45EA-8E8E-36C190665AA1}" name="Date" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{9BEAA38C-1BF4-46E1-BA17-94A51FB960F6}" name="User_ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{38C1138D-DBAA-490A-A7B6-EE2002F2DA9B}" name="Amount" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{AC0B7498-C7DE-41C1-B1F5-E95F722AB4AF}" name="Category" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{4BA09385-FEEE-454B-8BE7-CF2B831C26BB}" name="High_Value" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{43B3B1A1-A8DB-45EA-8E8E-36C190665AA1}" name="Date" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9BEAA38C-1BF4-46E1-BA17-94A51FB960F6}" name="User_ID" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{38C1138D-DBAA-490A-A7B6-EE2002F2DA9B}" name="Amount" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{AC0B7498-C7DE-41C1-B1F5-E95F722AB4AF}" name="Category" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{4BA09385-FEEE-454B-8BE7-CF2B831C26BB}" name="High_Value" dataDxfId="17">
       <calculatedColumnFormula>IF(Transactions_tbl[[#This Row],[Amount]]&gt;100,"Yes","No")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{81A82FB6-39DD-408C-9884-E3D906B0DDFE}" name="Category_Flag" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{81A82FB6-39DD-408C-9884-E3D906B0DDFE}" name="Category_Flag" dataDxfId="16">
       <calculatedColumnFormula>IF(Transactions_tbl[[#This Row],[Category]]="Crypto",1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9877,4 +11794,215 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE65FA1D-19DF-4F33-9493-2E6C5B4747B9}">
+  <dimension ref="A2:B7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="41"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="38">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="38">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="38">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="38">
+        <v>975</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF517D5-0F21-4A37-AA81-BBDFF67C7CFC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="39">
+        <v>820</v>
+      </c>
+      <c r="C3" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="39">
+        <v>80</v>
+      </c>
+      <c r="C4" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="39">
+        <v>75</v>
+      </c>
+      <c r="C5" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="39">
+        <v>975</v>
+      </c>
+      <c r="C6" s="40">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DEAD1D4-3316-4827-A49A-17F1084E2BCA}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="45"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="34">
+        <f>Analysis!A2</f>
+        <v>975</v>
+      </c>
+      <c r="C3" s="42">
+        <f>Analysis!B2</f>
+        <v>162.5</v>
+      </c>
+      <c r="F3" s="33">
+        <f>Analysis!C2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="34"/>
+      <c r="C4" s="42"/>
+      <c r="F4" s="33"/>
+    </row>
+    <row r="5" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+      <c r="C5" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C5:D5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>